--- a/examples/period-diff/规则_决策表.xlsx
+++ b/examples/period-diff/规则_决策表.xlsx
@@ -7,12 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="输入" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="设置" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="变量定义" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="字段组" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="决策表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="测试" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="设置" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="变量定义" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="字段组" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="决策表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="测试" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,12 +43,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,20 +95,20 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,7 +119,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -500,11 +499,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -514,82 +513,100 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>output/本期全量_更新后.xlsx</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>独有行</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>本期</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>本期全量.xlsx</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行 (加上下面追加的)。本期.存在 在追加来的行上是 否</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>追加</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>上期全量.xlsx</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>按 岗位编码 对齐; 独有行 = 追加: 上期有本期没有的岗位接到输出末尾, 同名列 (岗位名称 … 绩效) 带入, 本期独有的列为空</t>
         </is>
@@ -601,59 +618,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>设置项</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>output/本期全量_更新后.xlsx</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -668,52 +632,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>变量</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>定义</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="62" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>变更明细</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>差异(本期, 上期, 对比字段)</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>字段组 对比字段 里的每一列逐个比两期的同名列, 变化的拼成 字段:旧值-&gt;新值, 多个用 ; 接, 没有变化为空。相等判定与审计列同一套 (空串与空值相同, 文本严格比较); 空值显示为空串。第四个参数可改分隔符: 差异(本期, 上期, 对比字段, 分隔符="|")</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="5" t="n"/>
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="3" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>可用函数</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  日期(x)  如果(条件, 真值, 假值)  差异(新, 旧, 字段组)</t>
         </is>
@@ -724,7 +688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -739,34 +703,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>列名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>对比字段</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>岗位名称, 岗位职级, 一层组织, 拟任人, 绩效</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>两期要逐个比的列, 写一次; 改清单不碰表达式</t>
         </is>
@@ -777,7 +741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -797,17 +761,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>首次命中</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>四种差异互斥, 按顺序: 没了 / 新增 / 变了 / 没变</t>
         </is>
@@ -931,7 +895,7 @@
           <t>清空</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>追加来的行 (上期有本期没有): 本期.存在 是 否</t>
         </is>
@@ -971,7 +935,7 @@
           <t>清空</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>上期没有这个岗位</t>
         </is>
@@ -1011,7 +975,7 @@
           <t>变更明细</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>有字段变了: 把 差异() 算出来的明细写进去</t>
         </is>
@@ -1051,7 +1015,7 @@
           <t>清空</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>兜底: 两期都有且没变。变更字段明细 每次重算, 所以 D1 / D2 / D4 都显式清空</t>
         </is>
@@ -1062,7 +1026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1297,7 +1261,7 @@
           <t>岗位职级:21级-&gt;22级;绩效:A-&gt;B</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>两列变了, 按字段组顺序拼</t>
         </is>
@@ -1353,7 +1317,7 @@
           <t>空</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>上期没有; 变更字段明细 显式清空 (期望格写 空)</t>
         </is>
@@ -1425,7 +1389,7 @@
           <t>空</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>完全相同</t>
         </is>
@@ -1481,7 +1445,7 @@
           <t>空</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>追加来的行: 本期.存在 写 否 (没写默认是 是)</t>
         </is>
@@ -1541,7 +1505,7 @@
           <t>拟任人:李四-&gt;</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>新值为空显示为空串</t>
         </is>
@@ -1601,7 +1565,7 @@
           <t>拟任人:-&gt;王五</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>旧值为空显示为空串</t>
         </is>

--- a/examples/period-diff/规则_决策表.xlsx
+++ b/examples/period-diff/规则_决策表.xlsx
@@ -98,10 +98,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,114 +499,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30.4" customWidth="1" min="2" max="2"/>
+    <col width="8.600000000000001" customWidth="1" min="3" max="3"/>
+    <col width="8.600000000000001" customWidth="1" min="4" max="4"/>
+    <col width="15.8" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>设置项</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>每行一项: A 列名字 / B 列值 / 再往右是说明; 只认 基准日期 / 输出, 写别的加载时报错; B 列留空 = 取默认值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>output/本期全量_更新后.xlsx</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>输入表</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>下一行是列名, 之后每行声明一个输入: 名称 = 规则里的前缀; 匹配 = 主表写 主表, 其它写对齐到主表的键; 文件 = 默认文件 (命令行 -i 可覆盖)。输入表下面不要再写别的</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>独有行</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>本期</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>本期全量.xlsx</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行 (加上下面追加的)。本期.存在 在追加来的行上是 否</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>追加</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>上期全量.xlsx</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>按 岗位编码 对齐; 独有行 = 追加: 上期有本期没有的岗位接到输出末尾, 同名列 (岗位名称 … 绩效) 带入, 本期独有的列为空</t>
         </is>
@@ -627,7 +651,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -654,7 +678,7 @@
           <t>变更明细</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>差异(本期, 上期, 对比字段)</t>
         </is>
@@ -667,8 +691,8 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="2" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -676,7 +700,7 @@
           <t>可用函数</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
+      <c r="B4" s="3" t="n"/>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  日期(x)  如果(条件, 真值, 假值)  差异(新, 旧, 字段组)</t>
@@ -697,9 +721,9 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="10.8" customWidth="1" min="1" max="1"/>
+    <col width="47.4" customWidth="1" min="2" max="2"/>
+    <col width="47.8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -725,12 +749,12 @@
           <t>对比字段</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>岗位名称, 岗位职级, 一层组织, 拟任人, 绩效</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>两期要逐个比的列, 写一次; 改清单不碰表达式</t>
         </is>
@@ -750,13 +774,13 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10.8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11.8" customWidth="1" min="3" max="3"/>
+    <col width="11.8" customWidth="1" min="4" max="4"/>
+    <col width="10.8" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15.2" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -766,12 +790,12 @@
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>首次命中</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>四种差异互斥, 按顺序: 没了 / 新增 / 变了 / 没变</t>
         </is>
@@ -895,7 +919,7 @@
           <t>清空</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>追加来的行 (上期有本期没有): 本期.存在 是 否</t>
         </is>
@@ -935,7 +959,7 @@
           <t>清空</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>上期没有这个岗位</t>
         </is>
@@ -975,7 +999,7 @@
           <t>变更明细</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>有字段变了: 把 差异() 算出来的明细写进去</t>
         </is>
@@ -1036,19 +1060,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11.8" customWidth="1" min="2" max="2"/>
+    <col width="11.8" customWidth="1" min="3" max="3"/>
+    <col width="16.2" customWidth="1" min="4" max="4"/>
+    <col width="16.2" customWidth="1" min="5" max="5"/>
+    <col width="16.2" customWidth="1" min="6" max="6"/>
+    <col width="16.2" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="11.8" customWidth="1" min="10" max="10"/>
+    <col width="11.8" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="47" customWidth="1" min="14" max="14"/>
+    <col width="50.8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1261,7 +1285,7 @@
           <t>岗位职级:21级-&gt;22级;绩效:A-&gt;B</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>两列变了, 按字段组顺序拼</t>
         </is>
@@ -1317,7 +1341,7 @@
           <t>空</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>上期没有; 变更字段明细 显式清空 (期望格写 空)</t>
         </is>
@@ -1389,7 +1413,7 @@
           <t>空</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>完全相同</t>
         </is>
@@ -1445,7 +1469,7 @@
           <t>空</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>追加来的行: 本期.存在 写 否 (没写默认是 是)</t>
         </is>
@@ -1505,7 +1529,7 @@
           <t>拟任人:李四-&gt;</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>新值为空显示为空串</t>
         </is>
@@ -1565,7 +1589,7 @@
           <t>拟任人:-&gt;王五</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>旧值为空显示为空串</t>
         </is>

--- a/examples/period-diff/规则_决策表.xlsx
+++ b/examples/period-diff/规则_决策表.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,15 +31,27 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font/>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -67,7 +79,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -89,49 +101,104 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -510,133 +577,149 @@
     <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>设置项</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>每行一项: A 列名字 / B 列值 / 再往右是说明; 只认 基准日期 / 输出, 写别的加载时报错; B 列留空 = 取默认值</t>
         </is>
       </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>output/本期全量_更新后.xlsx</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖</t>
         </is>
       </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="5" t="n"/>
     </row>
     <row r="3"/>
-    <row r="4">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>输入表</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>下一行是列名, 之后每行声明一个输入: 名称 = 规则里的前缀; 匹配 = 主表写 主表, 其它写对齐到主表的键; 文件 = 默认文件 (命令行 -i 可覆盖)。输入表下面不要再写别的</t>
         </is>
       </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>独有行</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>本期</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>本期全量.xlsx</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行 (加上下面追加的)。本期.存在 在追加来的行上是 否</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>追加</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>上期全量.xlsx</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>按 岗位编码 对齐; 独有行 = 追加: 上期有本期没有的岗位接到输出末尾, 同名列 (岗位名称 … 绩效) 带入, 本期独有的列为空</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -656,52 +739,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>变量</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>定义</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="62" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>变更明细</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>差异(本期, 上期, 对比字段)</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>字段组 对比字段 里的每一列逐个比两期的同名列, 变化的拼成 字段:旧值-&gt;新值, 多个用 ; 接, 没有变化为空。相等判定与审计列同一套 (空串与空值相同, 文本严格比较); 空值显示为空串。第四个参数可改分隔符: 差异(本期, 上期, 对比字段, 分隔符="|")</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="2" t="n"/>
+      <c r="A3" s="6" t="n"/>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="10" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>可用函数</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  日期(x)  如果(条件, 真值, 假值)  差异(新, 旧, 字段组)</t>
         </is>
@@ -727,34 +810,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>列名</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>对比字段</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>岗位名称, 岗位职级, 一层组织, 拟任人, 绩效</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>两期要逐个比的列, 写一次; 改清单不碰表达式</t>
         </is>
@@ -785,267 +868,275 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>首次命中</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>四种差异互斥, 按顺序: 没了 / 新增 / 变了 / 没变</t>
         </is>
       </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>本期.存在</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>上期.存在</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>变更明细</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>差异类型</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>变更字段明细</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>REMOVED</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>清空</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>追加来的行 (上期有本期没有): 本期.存在 是 否</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>ADDED</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>清空</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>上期没有这个岗位</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>!= 空</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>变更明细</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>有字段变了: 把 差异() 算出来的明细写进去</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>清空</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>兜底: 两期都有且没变。变更字段明细 每次重算, 所以 D1 / D2 / D4 都显式清空</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:H1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1076,520 +1167,520 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>本期.存在</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>上期.存在</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>本期.岗位名称</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>上期.岗位名称</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>本期.岗位职级</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>上期.岗位职级</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>本期.拟任人</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>上期.拟任人</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>本期.绩效</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>上期.绩效</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>差异类型</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
+      <c r="M2" s="13" t="inlineStr">
         <is>
           <t>变更字段明细</t>
         </is>
       </c>
-      <c r="N2" s="9" t="inlineStr">
+      <c r="N2" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>财务部-部长</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>财务部-部长</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>22级</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>21级</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
       </c>
-      <c r="M3" s="13" t="inlineStr">
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>岗位职级:21级-&gt;22级;绩效:A-&gt;B</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>两列变了, 按字段组顺序拼</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>市场部-经理</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>19级</t>
         </is>
       </c>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-      <c r="I4" s="11" t="n"/>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="K4" s="16" t="n"/>
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>ADDED</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t>空</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>上期没有; 变更字段明细 显式清空 (期望格写 空)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>法务部-主管</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>法务部-主管</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>18级</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>18级</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>赵六</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>赵六</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="17" t="inlineStr">
         <is>
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="M5" s="17" t="inlineStr">
         <is>
           <t>空</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>完全相同</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>采购部-经理</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>20级</t>
         </is>
       </c>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>周七</t>
         </is>
       </c>
-      <c r="J6" s="11" t="n"/>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>REMOVED</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>空</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>追加来的行: 本期.存在 写 否 (没写默认是 是)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>人事部-部长</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>人事部-部长</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>20级</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>20级</t>
         </is>
       </c>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="J7" s="11" t="n"/>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="12" t="inlineStr">
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
       </c>
-      <c r="M7" s="12" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr">
         <is>
           <t>拟任人:李四-&gt;</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>新值为空显示为空串</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>人事部-部长</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>人事部-部长</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>20级</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>20级</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="11" t="n"/>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr">
+      <c r="M8" s="17" t="inlineStr">
         <is>
           <t>拟任人:-&gt;王五</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>旧值为空显示为空串</t>
         </is>
